--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/4420-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/4420-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A97C582B-6E72-4710-B562-FD8D86E4E438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF5168A4-1819-4125-B35D-4647EEC1168F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{79EDB4CD-3F77-4F6B-AD45-C2200258EB76}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{990651EE-BE80-4B0B-B5BD-D928307B7C6E}"/>
   </bookViews>
   <sheets>
     <sheet name="4420-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1517,30 +1517,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F28C843-5DB4-4BFF-8B26-94A321796FAC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{767185D8-4A90-4780-A477-2CC710130319}">
   <dimension ref="A1:X39"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1574,7 +1574,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1610,7 +1610,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1730,7 +1730,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2024</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>36.200000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2023</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2022</v>
       </c>
@@ -2240,7 +2240,7 @@
         <v>6.97</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2021</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2020</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2019</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>8.5399999999999991</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2018</v>
       </c>
@@ -2824,7 +2824,7 @@
         <v>5.33</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2017</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>5.87</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2016</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>4.82</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2015</v>
       </c>
@@ -3040,7 +3040,7 @@
         <v>6.07</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2014</v>
       </c>
@@ -3112,7 +3112,7 @@
         <v>4.3099999999999996</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2013</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2012</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>5.59</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2011</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>7.54</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2010</v>
       </c>
@@ -3400,7 +3400,7 @@
         <v>9.7100000000000009</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2009</v>
       </c>
@@ -3472,7 +3472,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2008</v>
       </c>
@@ -3544,7 +3544,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>2007</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2006</v>
       </c>
@@ -3688,7 +3688,7 @@
         <v>8.89</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>2005</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>9.68</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2004</v>
       </c>
@@ -3832,7 +3832,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>2003</v>
       </c>
@@ -3904,7 +3904,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>2002</v>
       </c>
@@ -3976,7 +3976,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="35">
         <v>2001</v>
       </c>
@@ -4048,7 +4048,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>2000</v>
       </c>
@@ -4120,7 +4120,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35">
         <v>1999</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37" t="s">
         <v>60</v>
       </c>
